--- a/genomics_dir/outputs/observation_period_anchored/omnibus_kw_1st_period_filter_1Mar22_2controls_18Jun26.xlsx
+++ b/genomics_dir/outputs/observation_period_anchored/omnibus_kw_1st_period_filter_1Mar22_2controls_18Jun26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imdea-my.sharepoint.com/personal/miksa_henkrich_nutricion_imdea_org/Documents/Escritorio/PNK/genomics_dir/outputs/observation_period_anchored/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_1EF137B9D7EF3C68537B3711595ED87656CD8FD8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C591025-6E76-43D4-BAB4-F432692C33F6}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="11_1EF137B9D7EF3C68537B3711595ED87656CD8FD8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEAF2D2-4A6B-4598-905D-3DCA3B80AF1D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1065" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kw_1st_obs_treated_only_period_" sheetId="1" r:id="rId1"/>
@@ -869,34 +869,6 @@
   </si>
   <si>
     <t>Personalized in 2nd month</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Outcomes when </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>receiving</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> personalization (only among personalized) </t>
-    </r>
   </si>
   <si>
     <r>
@@ -927,6 +899,40 @@
     </r>
   </si>
   <si>
+    <t>Treatment administration metadata &amp; timing of personalization delivery</t>
+  </si>
+  <si>
+    <t>Baseline characteristics &amp; Key outcomes</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Outcomes when </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>starting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> personalization (only among personalized) </t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Outcomes of the </t>
     </r>
@@ -940,7 +946,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>personalized</t>
+      <t>personalized phase</t>
     </r>
     <r>
       <rPr>
@@ -951,14 +957,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> phase (only among personalized) </t>
+      <t xml:space="preserve"> (only among personalized) </t>
     </r>
-  </si>
-  <si>
-    <t>Treatment administration metadata &amp; timing of personalization delivery</t>
-  </si>
-  <si>
-    <t>Baseline characteristics &amp; Key outcomes</t>
   </si>
 </sst>
 </file>
@@ -1183,43 +1183,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1246,6 +1213,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,6 +1269,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1560,1245 +1564,1245 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" style="11" customWidth="1"/>
-    <col min="3" max="8" width="19.44140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="5" customWidth="1"/>
+    <col min="3" max="8" width="19.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="14" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="26"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="33"/>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5" s="17">
+        <v>1.0749710790795401E-14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0.37903645896089672</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H8" s="17">
+        <v>0.55021994469801649</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H9" s="17">
+        <v>3.663276788411566E-44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="H10" s="17">
+        <v>1.6473160526614689E-48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H11" s="17">
+        <v>3.4355329815958201E-16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="H12" s="17">
+        <v>3.663276788411566E-44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H13" s="17">
+        <v>1.2211094479429479E-175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0.65228503874786026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="25"/>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28"/>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0.72578683346296424</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0.72295306588478814</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0.24778097658617729</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0.18765084135737389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="17">
+        <v>2.2292203914215751E-38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="17">
+        <v>1.8865612357330258E-14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="17">
+        <v>8.6661635544777173E-27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1.31715715161981E-18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="17">
+        <v>2.6841348684250138E-21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="17">
+        <v>2.4579806828108761E-19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="17">
+        <v>8.3816251797648294E-25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" s="18">
+        <v>0.64111531020855039</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="18">
+        <v>0.76681903454608091</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H30" s="17">
+        <v>0.66600463190160886</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="17">
+        <v>0.78931595780525243</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="17">
+        <v>2.8435198675119441E-21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="18">
+        <v>0.72295306588478814</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" s="17">
+        <v>9.7639511996319126E-5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H37" s="17">
+        <v>2.599924188807704E-58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38" s="17">
+        <v>1.6875844346134049E-58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="H39" s="17">
+        <v>3.5866543248127648E-43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H40" s="17">
+        <v>2.6694265493887332E-42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
-    </row>
-    <row r="4" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="H5" s="28">
-        <v>1.0749710790795401E-14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="H6" s="28"/>
-    </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="H7" s="28">
-        <v>0.37903645896089672</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="H8" s="28">
-        <v>0.55021994469801649</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="H9" s="28">
-        <v>3.663276788411566E-44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="H10" s="28">
-        <v>1.6473160526614689E-48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="H11" s="28">
-        <v>3.4355329815958201E-16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="H12" s="28">
-        <v>3.663276788411566E-44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="H13" s="28">
-        <v>1.2211094479429479E-175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="H14" s="29">
-        <v>0.65228503874786026</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="25"/>
+    </row>
+    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="26"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="28"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H43" s="17">
+        <v>6.5361198344740697E-6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="17">
+        <v>1.8991222148712121E-81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" s="17">
+        <v>3.692367497890806E-95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="H46" s="17">
+        <v>8.5162256424817303E-47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H47" s="17">
+        <v>8.4867460523054688E-64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="28">
-        <v>0.72578683346296424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="28">
-        <v>0.72295306588478814</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="28">
-        <v>0.24778097658617729</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="28">
-        <v>0.18765084135737389</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="28">
-        <v>2.2292203914215751E-38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="28">
-        <v>1.8865612357330258E-14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" s="28">
-        <v>8.6661635544777173E-27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="28">
-        <v>1.31715715161981E-18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="28">
-        <v>2.6841348684250138E-21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="28">
-        <v>2.4579806828108761E-19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="28">
-        <v>8.3816251797648294E-25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="29">
-        <v>0.64111531020855039</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H29" s="29">
-        <v>0.76681903454608091</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="28">
-        <v>0.66600463190160886</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H31" s="28">
-        <v>0.78931595780525243</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="28">
-        <v>2.8435198675119441E-21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" s="29">
-        <v>0.72295306588478814</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="H36" s="28">
-        <v>9.7639511996319126E-5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="H37" s="28">
-        <v>2.599924188807704E-58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="H38" s="28">
-        <v>1.6875844346134049E-58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="H39" s="28">
-        <v>3.5866543248127648E-43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G40" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H40" s="28">
-        <v>2.6694265493887332E-42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="28">
-        <v>6.5361198344740697E-6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="G44" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H44" s="28">
-        <v>1.8991222148712121E-81</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="H45" s="28">
-        <v>3.692367497890806E-95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="G46" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="H46" s="28">
-        <v>8.5162256424817303E-47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H47" s="28">
-        <v>8.4867460523054688E-64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="5"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="25"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="8"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="28"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="27" t="s">
+      <c r="A50" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="17">
         <v>1.1290754673151019E-25</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="H51" s="28">
+      <c r="H51" s="17">
         <v>8.398484551822201E-25</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H52" s="28">
+      <c r="H52" s="17">
         <v>1.0633809919169641E-27</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H53" s="28">
+      <c r="H53" s="17">
         <v>3.1499496324027369E-26</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H54" s="28">
+      <c r="H54" s="17">
         <v>2.8039261186208138E-23</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="F55" s="10" t="s">
+      <c r="F55" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="H55" s="28">
+      <c r="H55" s="17">
         <v>2.1584926225974992E-22</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="27" t="s">
+      <c r="A56" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="H56" s="28">
+      <c r="H56" s="17">
         <v>8.7640256143642322E-23</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="27" t="s">
+      <c r="A57" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H57" s="28">
+      <c r="H57" s="17">
         <v>1.610682911071602E-19</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F58" s="10" t="s">
+      <c r="F58" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="H58" s="28">
+      <c r="H58" s="17">
         <v>7.3374429625650331E-19</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32" t="s">
+      <c r="B59" s="20"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="E59" s="32" t="s">
+      <c r="E59" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="F59" s="32" t="s">
+      <c r="F59" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="G59" s="32" t="s">
+      <c r="G59" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="22">
         <v>1.813100387012163E-18</v>
       </c>
     </row>
@@ -2810,7 +2814,7 @@
     <mergeCell ref="A41:H42"/>
     <mergeCell ref="A34:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="H36:H40 H43:H47 H72:H1048576 H17:H33 H1:H14 H50:H59">
+  <conditionalFormatting sqref="H1:H14 H17:H33 H36:H40 H43:H47 H50:H59 H72:H1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
